--- a/CARGO_ARRIVAL_MORNING.xlsx
+++ b/CARGO_ARRIVAL_MORNING.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fiona\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\fiona\optimisation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A54CA0-97E5-4E61-B32E-FD3B49D00AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAF524C-F8E5-498A-B80F-95EE91CB30C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C96D902-8C59-4966-B0F7-AE5ADA9D8A6E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{4C96D902-8C59-4966-B0F7-AE5ADA9D8A6E}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="34">
   <si>
     <t>Morning</t>
   </si>
@@ -151,7 +151,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-14809]hh:mm;@"/>
+    <numFmt numFmtId="164" formatCode="[$-14809]hh:mm;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -520,13 +520,13 @@
   </cellStyleXfs>
   <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -623,22 +623,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -650,11 +641,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="144">
+  <dxfs count="74">
     <dxf>
       <fill>
         <patternFill>
@@ -736,202 +736,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1274,13 +1078,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="2" tint="-9.9948118533890809E-2"/>
         </patternFill>
       </fill>
@@ -1352,293 +1149,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2298,57 +1808,57 @@
       </c>
     </row>
     <row r="2" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="39"/>
-      <c r="AH2" s="39"/>
-      <c r="AI2" s="39"/>
-      <c r="AJ2" s="39"/>
-      <c r="AK2" s="39"/>
-      <c r="AL2" s="39"/>
-      <c r="AM2" s="39"/>
-      <c r="AN2" s="39"/>
-      <c r="AO2" s="39"/>
-      <c r="AP2" s="39"/>
-      <c r="AQ2" s="39"/>
-      <c r="AR2" s="39"/>
-      <c r="AS2" s="39"/>
-      <c r="AT2" s="39"/>
-      <c r="AU2" s="39"/>
-      <c r="AV2" s="39"/>
-      <c r="AW2" s="40"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="45"/>
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="45"/>
+      <c r="AK2" s="45"/>
+      <c r="AL2" s="45"/>
+      <c r="AM2" s="45"/>
+      <c r="AN2" s="45"/>
+      <c r="AO2" s="45"/>
+      <c r="AP2" s="45"/>
+      <c r="AQ2" s="45"/>
+      <c r="AR2" s="45"/>
+      <c r="AS2" s="45"/>
+      <c r="AT2" s="45"/>
+      <c r="AU2" s="45"/>
+      <c r="AV2" s="45"/>
+      <c r="AW2" s="46"/>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -3655,7 +3165,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="22" t="str">
-        <f t="shared" ref="C11:AW11" si="3">IF(E10=0, CONCATENATE(E9), CONCATENATE(E9, ",",E10))</f>
+        <f t="shared" ref="E11:AW11" si="3">IF(E10=0, CONCATENATE(E9), CONCATENATE(E9, ",",E10))</f>
         <v>6</v>
       </c>
       <c r="F11" s="22" t="str">
@@ -3836,57 +3346,57 @@
       </c>
     </row>
     <row r="12" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="39"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="39"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="39"/>
-      <c r="AR12" s="39"/>
-      <c r="AS12" s="39"/>
-      <c r="AT12" s="39"/>
-      <c r="AU12" s="39"/>
-      <c r="AV12" s="39"/>
-      <c r="AW12" s="40"/>
+      <c r="A12" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
+      <c r="Z12" s="45"/>
+      <c r="AA12" s="45"/>
+      <c r="AB12" s="45"/>
+      <c r="AC12" s="45"/>
+      <c r="AD12" s="45"/>
+      <c r="AE12" s="45"/>
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="45"/>
+      <c r="AH12" s="45"/>
+      <c r="AI12" s="45"/>
+      <c r="AJ12" s="45"/>
+      <c r="AK12" s="45"/>
+      <c r="AL12" s="45"/>
+      <c r="AM12" s="45"/>
+      <c r="AN12" s="45"/>
+      <c r="AO12" s="45"/>
+      <c r="AP12" s="45"/>
+      <c r="AQ12" s="45"/>
+      <c r="AR12" s="45"/>
+      <c r="AS12" s="45"/>
+      <c r="AT12" s="45"/>
+      <c r="AU12" s="45"/>
+      <c r="AV12" s="45"/>
+      <c r="AW12" s="46"/>
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
@@ -4307,7 +3817,7 @@
       <c r="AW18" s="34"/>
     </row>
     <row r="19" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="41" t="s">
+      <c r="A19" s="38" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="24">
@@ -4504,7 +4014,7 @@
       </c>
     </row>
     <row r="20" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="38" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="24">
@@ -4701,7 +4211,7 @@
       </c>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="38" t="s">
         <v>2</v>
       </c>
       <c r="B21" s="22" t="str">
@@ -4898,7 +4408,7 @@
       </c>
     </row>
     <row r="22" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="38" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="19" t="str">
@@ -4918,7 +4428,7 @@
         <v>6</v>
       </c>
       <c r="F22" s="19" t="str">
-        <f t="shared" ref="C22:AW22" si="8">IF(SUM(F10,F20) = 0, CONCATENATE(SUM(F9+F19)), CONCATENATE(SUM(F9,F19), ",", SUM(F10,F20)))</f>
+        <f t="shared" ref="F22:AW22" si="8">IF(SUM(F10,F20) = 0, CONCATENATE(SUM(F9+F19)), CONCATENATE(SUM(F9,F19), ",", SUM(F10,F20)))</f>
         <v>6</v>
       </c>
       <c r="G22" s="19" t="str">
@@ -5101,51 +4611,51 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A3:A4">
-    <cfRule type="expression" dxfId="101" priority="16">
+    <cfRule type="expression" dxfId="73" priority="16">
       <formula>#REF!&gt;=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:AW1">
+    <cfRule type="expression" dxfId="72" priority="57">
+      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="100" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
       <formula>"AL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="2" operator="equal">
       <formula>"Acar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="3" operator="equal">
       <formula>"AL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="4" operator="equal">
       <formula>"Acar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="5" operator="equal">
       <formula>"AL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="6" operator="equal">
       <formula>"Acar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="7" operator="equal">
       <formula>"AL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="8" operator="equal">
       <formula>"Acar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="9" operator="equal">
       <formula>"AL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="10" operator="equal">
       <formula>"Acar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="11" operator="equal">
       <formula>"AL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="12" operator="equal">
       <formula>"Acar6"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AW1">
-    <cfRule type="expression" dxfId="88" priority="57">
-      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5349,57 +4859,57 @@
       </c>
     </row>
     <row r="2" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="39"/>
-      <c r="AH2" s="39"/>
-      <c r="AI2" s="39"/>
-      <c r="AJ2" s="39"/>
-      <c r="AK2" s="39"/>
-      <c r="AL2" s="39"/>
-      <c r="AM2" s="39"/>
-      <c r="AN2" s="39"/>
-      <c r="AO2" s="39"/>
-      <c r="AP2" s="39"/>
-      <c r="AQ2" s="39"/>
-      <c r="AR2" s="39"/>
-      <c r="AS2" s="39"/>
-      <c r="AT2" s="39"/>
-      <c r="AU2" s="39"/>
-      <c r="AV2" s="39"/>
-      <c r="AW2" s="40"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="45"/>
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="45"/>
+      <c r="AK2" s="45"/>
+      <c r="AL2" s="45"/>
+      <c r="AM2" s="45"/>
+      <c r="AN2" s="45"/>
+      <c r="AO2" s="45"/>
+      <c r="AP2" s="45"/>
+      <c r="AQ2" s="45"/>
+      <c r="AR2" s="45"/>
+      <c r="AS2" s="45"/>
+      <c r="AT2" s="45"/>
+      <c r="AU2" s="45"/>
+      <c r="AV2" s="45"/>
+      <c r="AW2" s="46"/>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -6887,57 +6397,57 @@
       </c>
     </row>
     <row r="12" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="39"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="39"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="39"/>
-      <c r="AR12" s="39"/>
-      <c r="AS12" s="39"/>
-      <c r="AT12" s="39"/>
-      <c r="AU12" s="39"/>
-      <c r="AV12" s="39"/>
-      <c r="AW12" s="40"/>
+      <c r="A12" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
+      <c r="Z12" s="45"/>
+      <c r="AA12" s="45"/>
+      <c r="AB12" s="45"/>
+      <c r="AC12" s="45"/>
+      <c r="AD12" s="45"/>
+      <c r="AE12" s="45"/>
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="45"/>
+      <c r="AH12" s="45"/>
+      <c r="AI12" s="45"/>
+      <c r="AJ12" s="45"/>
+      <c r="AK12" s="45"/>
+      <c r="AL12" s="45"/>
+      <c r="AM12" s="45"/>
+      <c r="AN12" s="45"/>
+      <c r="AO12" s="45"/>
+      <c r="AP12" s="45"/>
+      <c r="AQ12" s="45"/>
+      <c r="AR12" s="45"/>
+      <c r="AS12" s="45"/>
+      <c r="AT12" s="45"/>
+      <c r="AU12" s="45"/>
+      <c r="AV12" s="45"/>
+      <c r="AW12" s="46"/>
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
@@ -7322,7 +6832,7 @@
       <c r="AW18" s="34"/>
     </row>
     <row r="19" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="41" t="s">
+      <c r="A19" s="38" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="24">
@@ -7519,7 +7029,7 @@
       </c>
     </row>
     <row r="20" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="38" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="24">
@@ -7716,7 +7226,7 @@
       </c>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="38" t="s">
         <v>2</v>
       </c>
       <c r="B21" s="22" t="str">
@@ -7913,7 +7423,7 @@
       </c>
     </row>
     <row r="22" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="38" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="19" t="str">
@@ -8025,7 +7535,7 @@
         <v>6</v>
       </c>
       <c r="AC22" s="19" t="str">
-        <f t="shared" ref="C22:AW22" si="7">IF(SUM(AC10,AC20) = 0, CONCATENATE(SUM(AC9+AC19)), CONCATENATE(SUM(AC9,AC19), ",", SUM(AC10,AC20)))</f>
+        <f t="shared" ref="AC22:AW22" si="7">IF(SUM(AC10,AC20) = 0, CONCATENATE(SUM(AC9+AC19)), CONCATENATE(SUM(AC9,AC19), ",", SUM(AC10,AC20)))</f>
         <v>6</v>
       </c>
       <c r="AD22" s="19" t="str">
@@ -8115,40 +7625,40 @@
     <mergeCell ref="A2:AW2"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="87" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="1" operator="equal">
       <formula>"AL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="2" operator="equal">
       <formula>"Acar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
       <formula>"AL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="equal">
       <formula>"Acar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
       <formula>"AL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="6" operator="equal">
       <formula>"Acar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="7" operator="equal">
       <formula>"AL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="8" operator="equal">
       <formula>"Acar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="9" operator="equal">
       <formula>"AL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="10" operator="equal">
       <formula>"Acar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="11" operator="equal">
       <formula>"AL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="12" operator="equal">
       <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8353,57 +7863,57 @@
       </c>
     </row>
     <row r="2" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="39"/>
-      <c r="AH2" s="39"/>
-      <c r="AI2" s="39"/>
-      <c r="AJ2" s="39"/>
-      <c r="AK2" s="39"/>
-      <c r="AL2" s="39"/>
-      <c r="AM2" s="39"/>
-      <c r="AN2" s="39"/>
-      <c r="AO2" s="39"/>
-      <c r="AP2" s="39"/>
-      <c r="AQ2" s="39"/>
-      <c r="AR2" s="39"/>
-      <c r="AS2" s="39"/>
-      <c r="AT2" s="39"/>
-      <c r="AU2" s="39"/>
-      <c r="AV2" s="39"/>
-      <c r="AW2" s="40"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="45"/>
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="45"/>
+      <c r="AK2" s="45"/>
+      <c r="AL2" s="45"/>
+      <c r="AM2" s="45"/>
+      <c r="AN2" s="45"/>
+      <c r="AO2" s="45"/>
+      <c r="AP2" s="45"/>
+      <c r="AQ2" s="45"/>
+      <c r="AR2" s="45"/>
+      <c r="AS2" s="45"/>
+      <c r="AT2" s="45"/>
+      <c r="AU2" s="45"/>
+      <c r="AV2" s="45"/>
+      <c r="AW2" s="46"/>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -9891,57 +9401,57 @@
       </c>
     </row>
     <row r="12" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="39"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="39"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="39"/>
-      <c r="AR12" s="39"/>
-      <c r="AS12" s="39"/>
-      <c r="AT12" s="39"/>
-      <c r="AU12" s="39"/>
-      <c r="AV12" s="39"/>
-      <c r="AW12" s="40"/>
+      <c r="A12" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
+      <c r="Z12" s="45"/>
+      <c r="AA12" s="45"/>
+      <c r="AB12" s="45"/>
+      <c r="AC12" s="45"/>
+      <c r="AD12" s="45"/>
+      <c r="AE12" s="45"/>
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="45"/>
+      <c r="AH12" s="45"/>
+      <c r="AI12" s="45"/>
+      <c r="AJ12" s="45"/>
+      <c r="AK12" s="45"/>
+      <c r="AL12" s="45"/>
+      <c r="AM12" s="45"/>
+      <c r="AN12" s="45"/>
+      <c r="AO12" s="45"/>
+      <c r="AP12" s="45"/>
+      <c r="AQ12" s="45"/>
+      <c r="AR12" s="45"/>
+      <c r="AS12" s="45"/>
+      <c r="AT12" s="45"/>
+      <c r="AU12" s="45"/>
+      <c r="AV12" s="45"/>
+      <c r="AW12" s="46"/>
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
@@ -11120,7 +10630,7 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="AW22" s="42" t="str">
+      <c r="AW22" s="39" t="str">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
@@ -11131,40 +10641,40 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="75" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="equal">
       <formula>"AL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="equal">
       <formula>"Acar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="3" operator="equal">
       <formula>"AL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="4" operator="equal">
       <formula>"Acar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="5" operator="equal">
       <formula>"AL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="6" operator="equal">
       <formula>"Acar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="7" operator="equal">
       <formula>"AL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="8" operator="equal">
       <formula>"Acar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="9" operator="equal">
       <formula>"AL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="10" operator="equal">
       <formula>"Acar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="11" operator="equal">
       <formula>"AL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="12" operator="equal">
       <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11369,57 +10879,57 @@
       </c>
     </row>
     <row r="2" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="39"/>
-      <c r="AH2" s="39"/>
-      <c r="AI2" s="39"/>
-      <c r="AJ2" s="39"/>
-      <c r="AK2" s="39"/>
-      <c r="AL2" s="39"/>
-      <c r="AM2" s="39"/>
-      <c r="AN2" s="39"/>
-      <c r="AO2" s="39"/>
-      <c r="AP2" s="39"/>
-      <c r="AQ2" s="39"/>
-      <c r="AR2" s="39"/>
-      <c r="AS2" s="39"/>
-      <c r="AT2" s="39"/>
-      <c r="AU2" s="39"/>
-      <c r="AV2" s="39"/>
-      <c r="AW2" s="40"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="45"/>
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="45"/>
+      <c r="AK2" s="45"/>
+      <c r="AL2" s="45"/>
+      <c r="AM2" s="45"/>
+      <c r="AN2" s="45"/>
+      <c r="AO2" s="45"/>
+      <c r="AP2" s="45"/>
+      <c r="AQ2" s="45"/>
+      <c r="AR2" s="45"/>
+      <c r="AS2" s="45"/>
+      <c r="AT2" s="45"/>
+      <c r="AU2" s="45"/>
+      <c r="AV2" s="45"/>
+      <c r="AW2" s="46"/>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -12907,57 +12417,57 @@
       </c>
     </row>
     <row r="12" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="39"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="39"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="39"/>
-      <c r="AR12" s="39"/>
-      <c r="AS12" s="39"/>
-      <c r="AT12" s="39"/>
-      <c r="AU12" s="39"/>
-      <c r="AV12" s="39"/>
-      <c r="AW12" s="40"/>
+      <c r="A12" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
+      <c r="Z12" s="45"/>
+      <c r="AA12" s="45"/>
+      <c r="AB12" s="45"/>
+      <c r="AC12" s="45"/>
+      <c r="AD12" s="45"/>
+      <c r="AE12" s="45"/>
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="45"/>
+      <c r="AH12" s="45"/>
+      <c r="AI12" s="45"/>
+      <c r="AJ12" s="45"/>
+      <c r="AK12" s="45"/>
+      <c r="AL12" s="45"/>
+      <c r="AM12" s="45"/>
+      <c r="AN12" s="45"/>
+      <c r="AO12" s="45"/>
+      <c r="AP12" s="45"/>
+      <c r="AQ12" s="45"/>
+      <c r="AR12" s="45"/>
+      <c r="AS12" s="45"/>
+      <c r="AT12" s="45"/>
+      <c r="AU12" s="45"/>
+      <c r="AV12" s="45"/>
+      <c r="AW12" s="46"/>
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
@@ -14148,7 +13658,7 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="AW22" s="42" t="str">
+      <c r="AW22" s="39" t="str">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
@@ -14159,40 +13669,40 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>"AL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
       <formula>"Acar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
       <formula>"AL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
       <formula>"Acar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="5" operator="equal">
       <formula>"AL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="6" operator="equal">
       <formula>"Acar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="7" operator="equal">
       <formula>"AL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="8" operator="equal">
       <formula>"Acar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="9" operator="equal">
       <formula>"AL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="10" operator="equal">
       <formula>"Acar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="11" operator="equal">
       <formula>"AL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
       <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14371,66 +13881,66 @@
       </c>
     </row>
     <row r="2" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="39"/>
-      <c r="AH2" s="39"/>
-      <c r="AI2" s="39"/>
-      <c r="AJ2" s="39"/>
-      <c r="AK2" s="39"/>
-      <c r="AL2" s="39"/>
-      <c r="AM2" s="39"/>
-      <c r="AN2" s="39"/>
-      <c r="AO2" s="39"/>
-      <c r="AP2" s="39"/>
-      <c r="AQ2" s="39"/>
-      <c r="AR2" s="39"/>
-      <c r="AS2" s="39"/>
-      <c r="AT2" s="39"/>
-      <c r="AU2" s="39"/>
-      <c r="AV2" s="39"/>
-      <c r="AW2" s="40"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="45"/>
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="45"/>
+      <c r="AK2" s="45"/>
+      <c r="AL2" s="45"/>
+      <c r="AM2" s="45"/>
+      <c r="AN2" s="45"/>
+      <c r="AO2" s="45"/>
+      <c r="AP2" s="45"/>
+      <c r="AQ2" s="45"/>
+      <c r="AR2" s="45"/>
+      <c r="AS2" s="45"/>
+      <c r="AT2" s="45"/>
+      <c r="AU2" s="45"/>
+      <c r="AV2" s="45"/>
+      <c r="AW2" s="46"/>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="27" t="s">
+      <c r="B3" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="41" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="28" t="s">
@@ -14576,10 +14086,10 @@
       <c r="A4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="30" t="s">
+      <c r="B4" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="42" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="26" t="s">
@@ -14725,10 +14235,10 @@
       <c r="A5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="30" t="s">
+      <c r="B5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="42" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="26" t="s">
@@ -14874,10 +14384,10 @@
       <c r="A6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="42" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="26" t="s">
@@ -15023,10 +14533,10 @@
       <c r="A7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="30" t="s">
+      <c r="B7" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="42" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="26" t="s">
@@ -15169,13 +14679,11 @@
       </c>
     </row>
     <row r="8" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="32"/>
+      <c r="A8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="33"/>
+      <c r="C8" s="43"/>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
       <c r="F8" s="33"/>
@@ -15224,198 +14732,198 @@
       <c r="AW8" s="34"/>
     </row>
     <row r="9" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="24">
         <f>SUM(COUNTIF(B3:B8,"=AL*"))</f>
-        <v>6</v>
-      </c>
-      <c r="C9" s="22">
+        <v>5</v>
+      </c>
+      <c r="C9" s="24">
         <f t="shared" ref="C9:AW9" si="0">SUM(COUNTIF(C3:C8,"=AL*"))</f>
         <v>5</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="I9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="L9" s="22">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="M9" s="22">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="N9" s="22">
+      <c r="H9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="L9" s="24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="M9" s="24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="N9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O9" s="22">
+      <c r="O9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="P9" s="22">
+      <c r="P9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="Q9" s="22">
+      <c r="Q9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="R9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="S9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="U9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="V9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="W9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="X9" s="22">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="Y9" s="22">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="Z9" s="22">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AA9" s="22">
+      <c r="R9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="U9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="V9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="W9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X9" s="24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Y9" s="24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Z9" s="24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AA9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AB9" s="22">
+      <c r="AB9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AC9" s="22">
+      <c r="AC9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AD9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AE9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AF9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AG9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AH9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AI9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AJ9" s="22">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AK9" s="22">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AL9" s="22">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AM9" s="22">
+      <c r="AD9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AE9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AF9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AG9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AH9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AI9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AJ9" s="24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AK9" s="24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AL9" s="24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AM9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AN9" s="22">
+      <c r="AN9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AO9" s="22">
+      <c r="AO9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AP9" s="22">
+      <c r="AP9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AQ9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AR9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AS9" s="22">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AT9" s="22">
+      <c r="AQ9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AR9" s="24">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AS9" s="24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AT9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AU9" s="22">
+      <c r="AU9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AV9" s="22">
+      <c r="AV9" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AW9" s="23">
+      <c r="AW9" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -15623,7 +15131,7 @@
       </c>
       <c r="B11" s="22" t="str">
         <f>IF(B10=0, CONCATENATE(B9), CONCATENATE(B9, ",",B10))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="22" t="str">
         <f t="shared" ref="C11:AW11" si="2">IF(C10=0, CONCATENATE(C9), CONCATENATE(C9, ",",C10))</f>
@@ -15815,64 +15323,64 @@
       </c>
     </row>
     <row r="12" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="39"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="39"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="39"/>
-      <c r="AR12" s="39"/>
-      <c r="AS12" s="39"/>
-      <c r="AT12" s="39"/>
-      <c r="AU12" s="39"/>
-      <c r="AV12" s="39"/>
-      <c r="AW12" s="40"/>
+      <c r="A12" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
+      <c r="Z12" s="45"/>
+      <c r="AA12" s="45"/>
+      <c r="AB12" s="45"/>
+      <c r="AC12" s="45"/>
+      <c r="AD12" s="45"/>
+      <c r="AE12" s="45"/>
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="45"/>
+      <c r="AH12" s="45"/>
+      <c r="AI12" s="45"/>
+      <c r="AJ12" s="45"/>
+      <c r="AK12" s="45"/>
+      <c r="AL12" s="45"/>
+      <c r="AM12" s="45"/>
+      <c r="AN12" s="45"/>
+      <c r="AO12" s="45"/>
+      <c r="AP12" s="45"/>
+      <c r="AQ12" s="45"/>
+      <c r="AR12" s="45"/>
+      <c r="AS12" s="45"/>
+      <c r="AT12" s="45"/>
+      <c r="AU12" s="45"/>
+      <c r="AV12" s="45"/>
+      <c r="AW12" s="46"/>
     </row>
     <row r="13" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="28"/>
-      <c r="C13" s="44"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
       <c r="F13" s="28"/>
@@ -15979,7 +15487,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="26"/>
-      <c r="C14" s="45"/>
+      <c r="C14" s="42"/>
       <c r="D14" s="26"/>
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
@@ -16066,7 +15574,7 @@
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="26"/>
-      <c r="C15" s="45"/>
+      <c r="C15" s="42"/>
       <c r="D15" s="26"/>
       <c r="E15" s="26"/>
       <c r="F15" s="26"/>
@@ -16117,7 +15625,7 @@
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="26"/>
-      <c r="C16" s="45"/>
+      <c r="C16" s="42"/>
       <c r="D16" s="26"/>
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
@@ -16168,7 +15676,7 @@
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="26"/>
-      <c r="C17" s="45"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="26"/>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
@@ -16219,7 +15727,7 @@
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="33"/>
-      <c r="C18" s="46"/>
+      <c r="C18" s="43"/>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
       <c r="F18" s="33"/>
@@ -16864,7 +16372,7 @@
       </c>
       <c r="B22" s="21" t="str">
         <f>IF(SUM(B10,B20) = 0, CONCATENATE(SUM(B9+B19)), CONCATENATE(SUM(B9,B19), ",", SUM(B10,B20)))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="21" t="str">
         <f t="shared" ref="C22:AW22" si="6">IF(SUM(C10,C20) = 0, CONCATENATE(SUM(C9+C19)), CONCATENATE(SUM(C9,C19), ",", SUM(C10,C20)))</f>
@@ -17050,7 +16558,7 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="AW22" s="42" t="str">
+      <c r="AW22" s="39" t="str">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
@@ -17060,41 +16568,41 @@
     <mergeCell ref="A2:AW2"/>
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="51" priority="1" operator="equal">
+  <conditionalFormatting sqref="B13:AW20 B3:AW10">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"AL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
       <formula>"Acar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
       <formula>"AL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
       <formula>"Acar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
       <formula>"AL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
       <formula>"Acar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
       <formula>"AL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
       <formula>"Acar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
       <formula>"AL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
       <formula>"Acar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
       <formula>"AL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
       <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17106,7 +16614,7 @@
           <x14:formula1>
             <xm:f>List!$F$2:$F$19</xm:f>
           </x14:formula1>
-          <xm:sqref>B3:AW8 B13:AW18</xm:sqref>
+          <xm:sqref>B13:AW18 B3:AW8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -17606,142 +17114,142 @@
       <c r="B4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="N4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="R4" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="S4" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="T4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="U4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="V4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="W4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="X4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB4" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC4" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD4" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AH4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AK4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AL4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AM4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AN4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AO4" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AQ4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AR4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AS4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AT4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU4" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AV4" s="43" t="s">
+      <c r="C4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="R4" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="S4" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="X4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB4" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC4" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO4" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU4" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV4" s="40" t="s">
         <v>23</v>
       </c>
       <c r="AW4" s="14" t="s">
@@ -17755,142 +17263,142 @@
       <c r="B5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="K5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="R5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="S5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="T5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="U5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="V5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="W5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="X5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AK5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AL5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AM5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AN5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AO5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AP5" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AQ5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AR5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AS5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AT5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AU5" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AV5" s="43" t="s">
+      <c r="C5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="S5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="T5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="U5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="V5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="W5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="X5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AM5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AN5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP5" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AS5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AT5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AU5" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="AV5" s="40" t="s">
         <v>24</v>
       </c>
       <c r="AW5" s="14" t="s">
@@ -17904,142 +17412,142 @@
       <c r="B6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="K6" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="P6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="R6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="S6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="T6" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="U6" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="V6" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="W6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="X6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE6" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF6" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG6" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP6" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AQ6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AR6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AS6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AT6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AU6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AV6" s="43" t="s">
+      <c r="C6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="R6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="T6" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="U6" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="V6" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="W6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="X6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE6" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG6" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP6" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AU6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AV6" s="40" t="s">
         <v>25</v>
       </c>
       <c r="AW6" s="14" t="s">
@@ -18053,142 +17561,142 @@
       <c r="B7" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="R7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="S7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="T7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="U7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="V7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="W7" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="X7" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y7" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH7" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI7" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ7" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AP7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AQ7" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="AR7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AS7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AT7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AU7" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="AV7" s="43" t="s">
+      <c r="C7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="R7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="S7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="T7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="U7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="V7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="W7" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH7" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI7" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ7" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ7" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AS7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AT7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AU7" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="AV7" s="40" t="s">
         <v>26</v>
       </c>
       <c r="AW7" s="14" t="s">
@@ -18936,57 +18444,57 @@
       </c>
     </row>
     <row r="12" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="39"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="39"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="39"/>
-      <c r="AR12" s="39"/>
-      <c r="AS12" s="39"/>
-      <c r="AT12" s="39"/>
-      <c r="AU12" s="39"/>
-      <c r="AV12" s="39"/>
-      <c r="AW12" s="40"/>
+      <c r="A12" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
+      <c r="Z12" s="45"/>
+      <c r="AA12" s="45"/>
+      <c r="AB12" s="45"/>
+      <c r="AC12" s="45"/>
+      <c r="AD12" s="45"/>
+      <c r="AE12" s="45"/>
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="45"/>
+      <c r="AH12" s="45"/>
+      <c r="AI12" s="45"/>
+      <c r="AJ12" s="45"/>
+      <c r="AK12" s="45"/>
+      <c r="AL12" s="45"/>
+      <c r="AM12" s="45"/>
+      <c r="AN12" s="45"/>
+      <c r="AO12" s="45"/>
+      <c r="AP12" s="45"/>
+      <c r="AQ12" s="45"/>
+      <c r="AR12" s="45"/>
+      <c r="AS12" s="45"/>
+      <c r="AT12" s="45"/>
+      <c r="AU12" s="45"/>
+      <c r="AV12" s="45"/>
+      <c r="AW12" s="46"/>
     </row>
     <row r="13" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -19100,259 +18608,259 @@
         <v>6</v>
       </c>
       <c r="B14" s="13"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="R14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="S14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="T14" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="U14" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="V14" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="W14" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="X14" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y14" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z14" s="43"/>
-      <c r="AA14" s="43"/>
-      <c r="AB14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE14" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF14" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG14" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH14" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI14" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ14" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="AK14" s="43"/>
-      <c r="AL14" s="43"/>
-      <c r="AM14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AP14" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="AQ14" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="AR14" s="43"/>
-      <c r="AS14" s="43"/>
-      <c r="AT14" s="43"/>
-      <c r="AU14" s="43"/>
-      <c r="AV14" s="43"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="R14" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="S14" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="T14" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="U14" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="V14" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="W14" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="X14" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y14" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z14" s="40"/>
+      <c r="AA14" s="40"/>
+      <c r="AB14" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC14" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD14" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE14" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF14" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG14" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH14" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI14" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ14" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK14" s="40"/>
+      <c r="AL14" s="40"/>
+      <c r="AM14" s="40"/>
+      <c r="AN14" s="40"/>
+      <c r="AO14" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP14" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ14" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR14" s="40"/>
+      <c r="AS14" s="40"/>
+      <c r="AT14" s="40"/>
+      <c r="AU14" s="40"/>
+      <c r="AV14" s="40"/>
       <c r="AW14" s="14"/>
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="13"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="43"/>
-      <c r="Y15" s="43"/>
-      <c r="Z15" s="43"/>
-      <c r="AA15" s="43"/>
-      <c r="AB15" s="43"/>
-      <c r="AC15" s="43"/>
-      <c r="AD15" s="43"/>
-      <c r="AE15" s="43"/>
-      <c r="AF15" s="43"/>
-      <c r="AG15" s="43"/>
-      <c r="AH15" s="43"/>
-      <c r="AI15" s="43"/>
-      <c r="AJ15" s="43"/>
-      <c r="AK15" s="43"/>
-      <c r="AL15" s="43"/>
-      <c r="AM15" s="43"/>
-      <c r="AN15" s="43"/>
-      <c r="AO15" s="43"/>
-      <c r="AP15" s="43"/>
-      <c r="AQ15" s="43"/>
-      <c r="AR15" s="43"/>
-      <c r="AS15" s="43"/>
-      <c r="AT15" s="43"/>
-      <c r="AU15" s="43"/>
-      <c r="AV15" s="43"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="40"/>
+      <c r="AB15" s="40"/>
+      <c r="AC15" s="40"/>
+      <c r="AD15" s="40"/>
+      <c r="AE15" s="40"/>
+      <c r="AF15" s="40"/>
+      <c r="AG15" s="40"/>
+      <c r="AH15" s="40"/>
+      <c r="AI15" s="40"/>
+      <c r="AJ15" s="40"/>
+      <c r="AK15" s="40"/>
+      <c r="AL15" s="40"/>
+      <c r="AM15" s="40"/>
+      <c r="AN15" s="40"/>
+      <c r="AO15" s="40"/>
+      <c r="AP15" s="40"/>
+      <c r="AQ15" s="40"/>
+      <c r="AR15" s="40"/>
+      <c r="AS15" s="40"/>
+      <c r="AT15" s="40"/>
+      <c r="AU15" s="40"/>
+      <c r="AV15" s="40"/>
       <c r="AW15" s="14"/>
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="13"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="43"/>
-      <c r="Y16" s="43"/>
-      <c r="Z16" s="43"/>
-      <c r="AA16" s="43"/>
-      <c r="AB16" s="43"/>
-      <c r="AC16" s="43"/>
-      <c r="AD16" s="43"/>
-      <c r="AE16" s="43"/>
-      <c r="AF16" s="43"/>
-      <c r="AG16" s="43"/>
-      <c r="AH16" s="43"/>
-      <c r="AI16" s="43"/>
-      <c r="AJ16" s="43"/>
-      <c r="AK16" s="43"/>
-      <c r="AL16" s="43"/>
-      <c r="AM16" s="43"/>
-      <c r="AN16" s="43"/>
-      <c r="AO16" s="43"/>
-      <c r="AP16" s="43"/>
-      <c r="AQ16" s="43"/>
-      <c r="AR16" s="43"/>
-      <c r="AS16" s="43"/>
-      <c r="AT16" s="43"/>
-      <c r="AU16" s="43"/>
-      <c r="AV16" s="43"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="40"/>
+      <c r="W16" s="40"/>
+      <c r="X16" s="40"/>
+      <c r="Y16" s="40"/>
+      <c r="Z16" s="40"/>
+      <c r="AA16" s="40"/>
+      <c r="AB16" s="40"/>
+      <c r="AC16" s="40"/>
+      <c r="AD16" s="40"/>
+      <c r="AE16" s="40"/>
+      <c r="AF16" s="40"/>
+      <c r="AG16" s="40"/>
+      <c r="AH16" s="40"/>
+      <c r="AI16" s="40"/>
+      <c r="AJ16" s="40"/>
+      <c r="AK16" s="40"/>
+      <c r="AL16" s="40"/>
+      <c r="AM16" s="40"/>
+      <c r="AN16" s="40"/>
+      <c r="AO16" s="40"/>
+      <c r="AP16" s="40"/>
+      <c r="AQ16" s="40"/>
+      <c r="AR16" s="40"/>
+      <c r="AS16" s="40"/>
+      <c r="AT16" s="40"/>
+      <c r="AU16" s="40"/>
+      <c r="AV16" s="40"/>
       <c r="AW16" s="14"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="13"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="43"/>
-      <c r="W17" s="43"/>
-      <c r="X17" s="43"/>
-      <c r="Y17" s="43"/>
-      <c r="Z17" s="43"/>
-      <c r="AA17" s="43"/>
-      <c r="AB17" s="43"/>
-      <c r="AC17" s="43"/>
-      <c r="AD17" s="43"/>
-      <c r="AE17" s="43"/>
-      <c r="AF17" s="43"/>
-      <c r="AG17" s="43"/>
-      <c r="AH17" s="43"/>
-      <c r="AI17" s="43"/>
-      <c r="AJ17" s="43"/>
-      <c r="AK17" s="43"/>
-      <c r="AL17" s="43"/>
-      <c r="AM17" s="43"/>
-      <c r="AN17" s="43"/>
-      <c r="AO17" s="43"/>
-      <c r="AP17" s="43"/>
-      <c r="AQ17" s="43"/>
-      <c r="AR17" s="43"/>
-      <c r="AS17" s="43"/>
-      <c r="AT17" s="43"/>
-      <c r="AU17" s="43"/>
-      <c r="AV17" s="43"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="40"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="40"/>
+      <c r="Y17" s="40"/>
+      <c r="Z17" s="40"/>
+      <c r="AA17" s="40"/>
+      <c r="AB17" s="40"/>
+      <c r="AC17" s="40"/>
+      <c r="AD17" s="40"/>
+      <c r="AE17" s="40"/>
+      <c r="AF17" s="40"/>
+      <c r="AG17" s="40"/>
+      <c r="AH17" s="40"/>
+      <c r="AI17" s="40"/>
+      <c r="AJ17" s="40"/>
+      <c r="AK17" s="40"/>
+      <c r="AL17" s="40"/>
+      <c r="AM17" s="40"/>
+      <c r="AN17" s="40"/>
+      <c r="AO17" s="40"/>
+      <c r="AP17" s="40"/>
+      <c r="AQ17" s="40"/>
+      <c r="AR17" s="40"/>
+      <c r="AS17" s="40"/>
+      <c r="AT17" s="40"/>
+      <c r="AU17" s="40"/>
+      <c r="AV17" s="40"/>
       <c r="AW17" s="14"/>
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20189,7 +19697,7 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="AW22" s="42" t="str">
+      <c r="AW22" s="39" t="str">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
@@ -20204,40 +19712,40 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"AL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"Acar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"AL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"Acar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"AL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"Acar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"AL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"Acar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
       <formula>"AL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
       <formula>"Acar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="11" operator="equal">
       <formula>"AL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
       <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
